--- a/Матрица_ИОТ_по_должностям_ШР_20.10.2026.xlsx
+++ b/Матрица_ИОТ_по_должностям_ШР_20.10.2026.xlsx
@@ -47,7 +47,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -71,7 +71,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -82,6 +82,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -149,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -196,6 +201,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -9742,17 +9750,17 @@
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46 (новый)</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>Отсутствует – разработать</t>
+          <t>Программа для линейных руководителей производства – разработать (новый п.46)</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>ИОТ-125 (распространить на руководителей производства) – требует решения</t>
+          <t>ИОТ-125 (п.1.2 – линейные руководители производства)</t>
         </is>
       </c>
       <c r="H86" s="10" t="inlineStr">
@@ -9815,7 +9823,7 @@
       <c r="BE86" s="8" t="inlineStr"/>
       <c r="BF86" s="8" t="inlineStr">
         <is>
-          <t>Нет в перечне (лин. руководитель)</t>
+          <t>ИОТ-125 распространена (лин. руководитель)</t>
         </is>
       </c>
       <c r="BG86" s="8" t="inlineStr"/>
@@ -9841,17 +9849,17 @@
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46 (новый)</t>
         </is>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>Отсутствует – разработать</t>
+          <t>Программа для линейных руководителей производства – разработать (новый п.46)</t>
         </is>
       </c>
       <c r="G87" s="10" t="inlineStr">
         <is>
-          <t>ИОТ-125 (распространить на руководителей производства) – требует решения</t>
+          <t>ИОТ-125 (п.1.2 – линейные руководители производства)</t>
         </is>
       </c>
       <c r="H87" s="10" t="inlineStr">
@@ -9914,7 +9922,7 @@
       <c r="BE87" s="8" t="inlineStr"/>
       <c r="BF87" s="8" t="inlineStr">
         <is>
-          <t>Нет в перечне (лин. руководитель)</t>
+          <t>ИОТ-125 распространена (лин. руководитель)</t>
         </is>
       </c>
       <c r="BG87" s="8" t="inlineStr"/>
@@ -11661,17 +11669,17 @@
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46 (новый)</t>
         </is>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>Отсутствует – разработать</t>
+          <t>Программа для линейных руководителей производства – разработать (новый п.46)</t>
         </is>
       </c>
       <c r="G103" s="10" t="inlineStr">
         <is>
-          <t>ИОТ-125 (распространить на руководителей производства) – требует решения</t>
+          <t>ИОТ-125 (п.1.2 – линейные руководители производства)</t>
         </is>
       </c>
       <c r="H103" s="10" t="inlineStr">
@@ -11734,7 +11742,7 @@
       <c r="BE103" s="8" t="inlineStr"/>
       <c r="BF103" s="8" t="inlineStr">
         <is>
-          <t>Нет в перечне (лин. руководитель)</t>
+          <t>ИОТ-125 распространена (лин. руководитель)</t>
         </is>
       </c>
       <c r="BG103" s="8" t="inlineStr"/>
@@ -13455,17 +13463,17 @@
       </c>
       <c r="E119" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46 (новый)</t>
         </is>
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
-          <t>Отсутствует – разработать</t>
+          <t>Программа для линейных руководителей производства – разработать (новый п.46)</t>
         </is>
       </c>
       <c r="G119" s="10" t="inlineStr">
         <is>
-          <t>ИОТ-125 (распространить на руководителей производства) – требует решения</t>
+          <t>ИОТ-125 (п.1.2 – линейные руководители производства)</t>
         </is>
       </c>
       <c r="H119" s="10" t="inlineStr">
@@ -13523,12 +13531,16 @@
       <c r="AZ119" s="8" t="inlineStr"/>
       <c r="BA119" s="8" t="inlineStr"/>
       <c r="BB119" s="8" t="inlineStr"/>
-      <c r="BC119" s="8" t="inlineStr"/>
+      <c r="BC119" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="BD119" s="8" t="inlineStr"/>
       <c r="BE119" s="8" t="inlineStr"/>
       <c r="BF119" s="8" t="inlineStr">
         <is>
-          <t>Нет в перечне (лин. руководитель)</t>
+          <t>ИОТ-125 распространена (лин. руководитель)</t>
         </is>
       </c>
       <c r="BG119" s="8" t="inlineStr"/>
@@ -13554,17 +13566,17 @@
       </c>
       <c r="E120" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46 (новый)</t>
         </is>
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t>Отсутствует – разработать</t>
+          <t>Программа для линейных руководителей производства – разработать (новый п.46)</t>
         </is>
       </c>
       <c r="G120" s="10" t="inlineStr">
         <is>
-          <t>ИОТ-125 (распространить на руководителей производства) – требует решения</t>
+          <t>ИОТ-125 (п.1.2 – линейные руководители производства)</t>
         </is>
       </c>
       <c r="H120" s="10" t="inlineStr">
@@ -13627,7 +13639,7 @@
       <c r="BE120" s="8" t="inlineStr"/>
       <c r="BF120" s="8" t="inlineStr">
         <is>
-          <t>Нет в перечне (лин. руководитель)</t>
+          <t>ИОТ-125 распространена (лин. руководитель)</t>
         </is>
       </c>
       <c r="BG120" s="8" t="inlineStr"/>
@@ -14451,17 +14463,17 @@
       </c>
       <c r="E127" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46 (новый)</t>
         </is>
       </c>
       <c r="F127" s="10" t="inlineStr">
         <is>
-          <t>Отсутствует – разработать</t>
+          <t>Программа для линейных руководителей производства – разработать (новый п.46)</t>
         </is>
       </c>
       <c r="G127" s="10" t="inlineStr">
         <is>
-          <t>ИОТ-125 (распространить на руководителей производства) – требует решения</t>
+          <t>ИОТ-125 (п.1.2 – линейные руководители производства)</t>
         </is>
       </c>
       <c r="H127" s="10" t="inlineStr">
@@ -14524,7 +14536,7 @@
       <c r="BE127" s="8" t="inlineStr"/>
       <c r="BF127" s="8" t="inlineStr">
         <is>
-          <t>Нет в перечне (лин. руководитель)</t>
+          <t>ИОТ-125 распространена (лин. руководитель)</t>
         </is>
       </c>
       <c r="BG127" s="8" t="inlineStr"/>
@@ -30476,17 +30488,17 @@
       </c>
       <c r="E288" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46 (новый)</t>
         </is>
       </c>
       <c r="F288" s="10" t="inlineStr">
         <is>
-          <t>Отсутствует – разработать</t>
+          <t>Программа для линейных руководителей производства – разработать (новый п.46)</t>
         </is>
       </c>
       <c r="G288" s="10" t="inlineStr">
         <is>
-          <t>ИОТ-125 (распространить на руководителей производства) – требует решения</t>
+          <t>ИОТ-125 (п.1.2 – линейные руководители производства)</t>
         </is>
       </c>
       <c r="H288" s="10" t="inlineStr">
@@ -30549,7 +30561,7 @@
       <c r="BE288" s="8" t="inlineStr"/>
       <c r="BF288" s="8" t="inlineStr">
         <is>
-          <t>Нет в перечне (лин. руководитель)</t>
+          <t>ИОТ-125 распространена (лин. руководитель)</t>
         </is>
       </c>
       <c r="BG288" s="8" t="inlineStr"/>
@@ -31595,17 +31607,17 @@
       </c>
       <c r="E297" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46 (новый)</t>
         </is>
       </c>
       <c r="F297" s="10" t="inlineStr">
         <is>
-          <t>Отсутствует – разработать</t>
+          <t>Программа для линейных руководителей производства – разработать (новый п.46)</t>
         </is>
       </c>
       <c r="G297" s="10" t="inlineStr">
         <is>
-          <t>ИОТ-125 (распространить на руководителей производства) – требует решения</t>
+          <t>ИОТ-125 (п.1.2 – линейные руководители производства)</t>
         </is>
       </c>
       <c r="H297" s="10" t="inlineStr">
@@ -31668,7 +31680,7 @@
       <c r="BE297" s="8" t="inlineStr"/>
       <c r="BF297" s="8" t="inlineStr">
         <is>
-          <t>Нет в перечне (лин. руководитель)</t>
+          <t>ИОТ-125 распространена (лин. руководитель)</t>
         </is>
       </c>
       <c r="BG297" s="8" t="inlineStr"/>
@@ -31944,17 +31956,17 @@
       </c>
       <c r="E300" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46 (новый)</t>
         </is>
       </c>
       <c r="F300" s="10" t="inlineStr">
         <is>
-          <t>Отсутствует – разработать</t>
+          <t>Программа для линейных руководителей производства – разработать (новый п.46)</t>
         </is>
       </c>
       <c r="G300" s="10" t="inlineStr">
         <is>
-          <t>ИОТ-125 (распространить на руководителей производства) – требует решения</t>
+          <t>ИОТ-125 (п.1.2 – линейные руководители производства)</t>
         </is>
       </c>
       <c r="H300" s="10" t="inlineStr">
@@ -32017,7 +32029,7 @@
       <c r="BE300" s="8" t="inlineStr"/>
       <c r="BF300" s="8" t="inlineStr">
         <is>
-          <t>Нет в перечне (лин. руководитель)</t>
+          <t>ИОТ-125 распространена (лин. руководитель)</t>
         </is>
       </c>
       <c r="BG300" s="8" t="inlineStr"/>
@@ -32043,17 +32055,17 @@
       </c>
       <c r="E301" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46 (новый)</t>
         </is>
       </c>
       <c r="F301" s="10" t="inlineStr">
         <is>
-          <t>Отсутствует – разработать</t>
+          <t>Программа для линейных руководителей производства – разработать (новый п.46)</t>
         </is>
       </c>
       <c r="G301" s="10" t="inlineStr">
         <is>
-          <t>ИОТ-125 (распространить на руководителей производства) – требует решения</t>
+          <t>ИОТ-125 (п.1.2 – линейные руководители производства)</t>
         </is>
       </c>
       <c r="H301" s="10" t="inlineStr">
@@ -32116,7 +32128,7 @@
       <c r="BE301" s="8" t="inlineStr"/>
       <c r="BF301" s="8" t="inlineStr">
         <is>
-          <t>Нет в перечне (лин. руководитель)</t>
+          <t>ИОТ-125 распространена (лин. руководитель)</t>
         </is>
       </c>
       <c r="BG301" s="8" t="inlineStr"/>
@@ -34065,17 +34077,17 @@
       </c>
       <c r="E317" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46 (новый)</t>
         </is>
       </c>
       <c r="F317" s="10" t="inlineStr">
         <is>
-          <t>Отсутствует – разработать</t>
+          <t>Программа для линейных руководителей производства – разработать (новый п.46)</t>
         </is>
       </c>
       <c r="G317" s="10" t="inlineStr">
         <is>
-          <t>ИОТ-125 (распространить на руководителей производства) – требует решения</t>
+          <t>ИОТ-125 (п.1.2 – линейные руководители производства)</t>
         </is>
       </c>
       <c r="H317" s="10" t="inlineStr">
@@ -34138,7 +34150,7 @@
       <c r="BE317" s="8" t="inlineStr"/>
       <c r="BF317" s="8" t="inlineStr">
         <is>
-          <t>Нет в перечне (лин. руководитель)</t>
+          <t>ИОТ-125 распространена (лин. руководитель)</t>
         </is>
       </c>
       <c r="BG317" s="8" t="inlineStr"/>
@@ -36477,17 +36489,17 @@
       </c>
       <c r="E335" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46 (новый)</t>
         </is>
       </c>
       <c r="F335" s="10" t="inlineStr">
         <is>
-          <t>Отсутствует – разработать</t>
+          <t>Программа для линейных руководителей производства – разработать (новый п.46)</t>
         </is>
       </c>
       <c r="G335" s="10" t="inlineStr">
         <is>
-          <t>ИОТ-125 (распространить на руководителей производства) – требует решения</t>
+          <t>ИОТ-125 (п.1.2 – линейные руководители производства)</t>
         </is>
       </c>
       <c r="H335" s="10" t="inlineStr">
@@ -36545,12 +36557,16 @@
       <c r="AZ335" s="8" t="inlineStr"/>
       <c r="BA335" s="8" t="inlineStr"/>
       <c r="BB335" s="8" t="inlineStr"/>
-      <c r="BC335" s="8" t="inlineStr"/>
+      <c r="BC335" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="BD335" s="8" t="inlineStr"/>
       <c r="BE335" s="8" t="inlineStr"/>
       <c r="BF335" s="8" t="inlineStr">
         <is>
-          <t>Нет в перечне (лин. руководитель)</t>
+          <t>ИОТ-125 распространена (лин. руководитель)</t>
         </is>
       </c>
       <c r="BG335" s="8" t="inlineStr"/>
@@ -38499,17 +38515,17 @@
       </c>
       <c r="E355" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46 (новый)</t>
         </is>
       </c>
       <c r="F355" s="10" t="inlineStr">
         <is>
-          <t>Отсутствует – разработать</t>
+          <t>Программа для линейных руководителей производства – разработать (новый п.46)</t>
         </is>
       </c>
       <c r="G355" s="10" t="inlineStr">
         <is>
-          <t>ИОТ-125 (распространить на руководителей производства) – требует решения</t>
+          <t>ИОТ-125 (п.1.2 – линейные руководители производства)</t>
         </is>
       </c>
       <c r="H355" s="10" t="inlineStr">
@@ -38567,12 +38583,16 @@
       <c r="AZ355" s="8" t="inlineStr"/>
       <c r="BA355" s="8" t="inlineStr"/>
       <c r="BB355" s="8" t="inlineStr"/>
-      <c r="BC355" s="8" t="inlineStr"/>
+      <c r="BC355" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="BD355" s="8" t="inlineStr"/>
       <c r="BE355" s="8" t="inlineStr"/>
       <c r="BF355" s="8" t="inlineStr">
         <is>
-          <t>Нет в перечне (лин. руководитель)</t>
+          <t>ИОТ-125 распространена (лин. руководитель)</t>
         </is>
       </c>
       <c r="BG355" s="8" t="inlineStr"/>
@@ -38997,17 +39017,17 @@
       </c>
       <c r="E359" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46 (новый)</t>
         </is>
       </c>
       <c r="F359" s="10" t="inlineStr">
         <is>
-          <t>Отсутствует – разработать</t>
+          <t>Программа для линейных руководителей производства – разработать (новый п.46)</t>
         </is>
       </c>
       <c r="G359" s="10" t="inlineStr">
         <is>
-          <t>ИОТ-125 (распространить на руководителей производства) – требует решения</t>
+          <t>ИОТ-125 (п.1.2 – линейные руководители производства)</t>
         </is>
       </c>
       <c r="H359" s="10" t="inlineStr">
@@ -39065,12 +39085,16 @@
       <c r="AZ359" s="8" t="inlineStr"/>
       <c r="BA359" s="8" t="inlineStr"/>
       <c r="BB359" s="8" t="inlineStr"/>
-      <c r="BC359" s="8" t="inlineStr"/>
+      <c r="BC359" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="BD359" s="8" t="inlineStr"/>
       <c r="BE359" s="8" t="inlineStr"/>
       <c r="BF359" s="8" t="inlineStr">
         <is>
-          <t>Нет в перечне (лин. руководитель)</t>
+          <t>ИОТ-125 распространена (лин. руководитель)</t>
         </is>
       </c>
       <c r="BG359" s="8" t="inlineStr"/>
@@ -39594,17 +39618,17 @@
       </c>
       <c r="E364" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46 (новый)</t>
         </is>
       </c>
       <c r="F364" s="10" t="inlineStr">
         <is>
-          <t>Отсутствует – разработать</t>
+          <t>Программа для линейных руководителей производства – разработать (новый п.46)</t>
         </is>
       </c>
       <c r="G364" s="10" t="inlineStr">
         <is>
-          <t>ИОТ-125 (распространить на руководителей производства) – требует решения</t>
+          <t>ИОТ-125 (п.1.2 – линейные руководители производства)</t>
         </is>
       </c>
       <c r="H364" s="10" t="inlineStr">
@@ -39667,7 +39691,7 @@
       <c r="BE364" s="8" t="inlineStr"/>
       <c r="BF364" s="8" t="inlineStr">
         <is>
-          <t>Нет в перечне (лин. руководитель)</t>
+          <t>ИОТ-125 распространена (лин. руководитель)</t>
         </is>
       </c>
       <c r="BG364" s="8" t="inlineStr"/>
@@ -39693,17 +39717,17 @@
       </c>
       <c r="E365" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46 (новый)</t>
         </is>
       </c>
       <c r="F365" s="10" t="inlineStr">
         <is>
-          <t>Отсутствует – разработать</t>
+          <t>Программа для линейных руководителей производства – разработать (новый п.46)</t>
         </is>
       </c>
       <c r="G365" s="10" t="inlineStr">
         <is>
-          <t>ИОТ-125 (распространить на руководителей производства) – требует решения</t>
+          <t>ИОТ-125 (п.1.2 – линейные руководители производства)</t>
         </is>
       </c>
       <c r="H365" s="10" t="inlineStr">
@@ -39766,7 +39790,7 @@
       <c r="BE365" s="8" t="inlineStr"/>
       <c r="BF365" s="8" t="inlineStr">
         <is>
-          <t>Нет в перечне (лин. руководитель)</t>
+          <t>ИОТ-125 распространена (лин. руководитель)</t>
         </is>
       </c>
       <c r="BG365" s="8" t="inlineStr"/>
@@ -40633,17 +40657,17 @@
       </c>
       <c r="E373" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46 (новый)</t>
         </is>
       </c>
       <c r="F373" s="10" t="inlineStr">
         <is>
-          <t>Отсутствует – разработать</t>
+          <t>Программа для линейных руководителей производства – разработать (новый п.46)</t>
         </is>
       </c>
       <c r="G373" s="10" t="inlineStr">
         <is>
-          <t>ИОТ-125 (распространить на руководителей производства) – требует решения</t>
+          <t>ИОТ-125 (п.1.2 – линейные руководители производства)</t>
         </is>
       </c>
       <c r="H373" s="10" t="inlineStr">
@@ -40706,7 +40730,7 @@
       <c r="BE373" s="8" t="inlineStr"/>
       <c r="BF373" s="8" t="inlineStr">
         <is>
-          <t>Нет в перечне (лин. руководитель)</t>
+          <t>ИОТ-125 распространена (лин. руководитель)</t>
         </is>
       </c>
       <c r="BG373" s="8" t="inlineStr"/>
@@ -40982,17 +41006,17 @@
       </c>
       <c r="E376" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46 (новый)</t>
         </is>
       </c>
       <c r="F376" s="10" t="inlineStr">
         <is>
-          <t>Отсутствует – разработать</t>
+          <t>Программа для линейных руководителей производства – разработать (новый п.46)</t>
         </is>
       </c>
       <c r="G376" s="10" t="inlineStr">
         <is>
-          <t>ИОТ-125 (распространить на руководителей производства) – требует решения</t>
+          <t>ИОТ-125 (п.1.2 – линейные руководители производства)</t>
         </is>
       </c>
       <c r="H376" s="10" t="inlineStr">
@@ -41055,7 +41079,7 @@
       <c r="BE376" s="8" t="inlineStr"/>
       <c r="BF376" s="8" t="inlineStr">
         <is>
-          <t>Нет в перечне (лин. руководитель)</t>
+          <t>ИОТ-125 распространена (лин. руководитель)</t>
         </is>
       </c>
       <c r="BG376" s="8" t="inlineStr"/>
@@ -42745,17 +42769,17 @@
       </c>
       <c r="E393" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46 (новый)</t>
         </is>
       </c>
       <c r="F393" s="10" t="inlineStr">
         <is>
-          <t>Отсутствует – разработать</t>
+          <t>Программа для линейных руководителей производства – разработать (новый п.46)</t>
         </is>
       </c>
       <c r="G393" s="10" t="inlineStr">
         <is>
-          <t>ИОТ-125 (распространить на руководителей производства) – требует решения</t>
+          <t>ИОТ-125 (п.1.2 – линейные руководители производства)</t>
         </is>
       </c>
       <c r="H393" s="10" t="inlineStr">
@@ -42818,7 +42842,7 @@
       <c r="BE393" s="8" t="inlineStr"/>
       <c r="BF393" s="8" t="inlineStr">
         <is>
-          <t>Нет в перечне (лин. руководитель)</t>
+          <t>ИОТ-125 распространена (лин. руководитель)</t>
         </is>
       </c>
       <c r="BG393" s="8" t="inlineStr"/>
@@ -43918,12 +43942,12 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Решить: распространить на руководителей производства</t>
+          <t>ВЫПОЛНЕНО 21.10.2026: распространена на линейных руководителей производства (проект ИОТ и приказа)</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Мастера, начальники участков, руководители цехов (24 чел.) не охвачены перечнем. Также подходит для специалиста по ПБ.</t>
+          <t>Внесены: п.1.1, 1.2 (перечень должностей), 1.3, 3.10.1 (обязанности), 3.13.2, 3.14.4 (СИЗ), 4.6 (перед сменой), 5.8 (во время работы), 7.5.2 (по окончании смены). Объём ИОТ – 16 л. (в приказе исправлено). Осталось: добавить в перечень новый п.46 «Линейные руководители производства» и разработать программу инструктажа.</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
@@ -44543,30 +44567,30 @@
       <c r="F13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>ИОТ-14</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>Инструкция по охране труда для монтажника электрооборудования летательных аппаратов (всех разрядов)</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>Профессиональная</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E14" s="10" t="n">
+      <c r="E14" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="10" t="inlineStr"/>
+      <c r="F14" s="18" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -44595,60 +44619,60 @@
       <c r="F15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>ИОТ-16</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Маляр (наименование в перечне не указано)</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>Профессиональная</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E16" s="10" t="n">
+      <c r="E16" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="18" t="inlineStr">
         <is>
           <t>Указан только номер в графе «Программа» п.17</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>ИОТ-17</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>Главный энергетик (наименование в перечне не указано)</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>Профессиональная</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E17" s="10" t="n">
+      <c r="E17" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="18" t="inlineStr">
         <is>
           <t>Указан только номер в графе «Программа» п.18</t>
         </is>
@@ -44993,30 +45017,30 @@
       <c r="F30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>ИОТ-33</t>
         </is>
       </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="B31" s="18" t="inlineStr">
         <is>
           <t>Инструкция по охране труда для столяра-краснодеревщика</t>
         </is>
       </c>
-      <c r="C31" s="10" t="inlineStr">
+      <c r="C31" s="18" t="inlineStr">
         <is>
           <t>Профессиональная</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr">
+      <c r="D31" s="18" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="E31" s="10" t="n">
+      <c r="E31" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F31" s="10" t="inlineStr"/>
+      <c r="F31" s="18" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -45175,56 +45199,56 @@
       <c r="F37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="18" t="inlineStr">
         <is>
           <t>ИОТ-40</t>
         </is>
       </c>
-      <c r="B38" s="10" t="inlineStr">
+      <c r="B38" s="18" t="inlineStr">
         <is>
           <t>Инструкция по охране труда для оператора листосгибочного оборудования (всех разрядов)</t>
         </is>
       </c>
-      <c r="C38" s="10" t="inlineStr">
+      <c r="C38" s="18" t="inlineStr">
         <is>
           <t>Профессиональная</t>
         </is>
       </c>
-      <c r="D38" s="10" t="inlineStr">
+      <c r="D38" s="18" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="E38" s="10" t="n">
+      <c r="E38" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F38" s="10" t="inlineStr"/>
+      <c r="F38" s="18" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="18" t="inlineStr">
         <is>
           <t>ИОТ-41</t>
         </is>
       </c>
-      <c r="B39" s="10" t="inlineStr">
+      <c r="B39" s="18" t="inlineStr">
         <is>
           <t>Инструкция по охране труда для оператора термопластавтомата (всех разрядов)</t>
         </is>
       </c>
-      <c r="C39" s="10" t="inlineStr">
+      <c r="C39" s="18" t="inlineStr">
         <is>
           <t>Профессиональная</t>
         </is>
       </c>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="D39" s="18" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="E39" s="10" t="n">
+      <c r="E39" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F39" s="10" t="inlineStr"/>
+      <c r="F39" s="18" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
@@ -45257,30 +45281,30 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="A41" s="18" t="inlineStr">
         <is>
           <t>ИОТ-43</t>
         </is>
       </c>
-      <c r="B41" s="10" t="inlineStr">
+      <c r="B41" s="18" t="inlineStr">
         <is>
           <t>Инструкция по охране труда для оператора лазерных установок (всех разрядов)</t>
         </is>
       </c>
-      <c r="C41" s="10" t="inlineStr">
+      <c r="C41" s="18" t="inlineStr">
         <is>
           <t>Профессиональная</t>
         </is>
       </c>
-      <c r="D41" s="10" t="inlineStr">
+      <c r="D41" s="18" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="E41" s="10" t="n">
+      <c r="E41" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F41" s="10" t="inlineStr"/>
+      <c r="F41" s="18" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -45931,30 +45955,30 @@
       <c r="F65" s="7" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="10" t="inlineStr">
+      <c r="A66" s="18" t="inlineStr">
         <is>
           <t>ИОТ-79</t>
         </is>
       </c>
-      <c r="B66" s="10" t="inlineStr">
+      <c r="B66" s="18" t="inlineStr">
         <is>
           <t>Инструкция по охране труда при работе на листогибочном прессе (станке)</t>
         </is>
       </c>
-      <c r="C66" s="10" t="inlineStr">
+      <c r="C66" s="18" t="inlineStr">
         <is>
           <t>По виду работ</t>
         </is>
       </c>
-      <c r="D66" s="10" t="inlineStr">
+      <c r="D66" s="18" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="E66" s="10" t="n">
+      <c r="E66" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F66" s="10" t="inlineStr"/>
+      <c r="F66" s="18" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
@@ -46039,30 +46063,30 @@
       <c r="F69" s="7" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="10" t="inlineStr">
+      <c r="A70" s="18" t="inlineStr">
         <is>
           <t>ИОТ-85</t>
         </is>
       </c>
-      <c r="B70" s="10" t="inlineStr">
+      <c r="B70" s="18" t="inlineStr">
         <is>
           <t>Инструкция по охране труда при работе на компрессорной установке</t>
         </is>
       </c>
-      <c r="C70" s="10" t="inlineStr">
+      <c r="C70" s="18" t="inlineStr">
         <is>
           <t>По виду работ</t>
         </is>
       </c>
-      <c r="D70" s="10" t="inlineStr">
+      <c r="D70" s="18" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="E70" s="10" t="n">
+      <c r="E70" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F70" s="10" t="inlineStr"/>
+      <c r="F70" s="18" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
